--- a/output/Pacdora_Leads_2026-03-02.xlsx
+++ b/output/Pacdora_Leads_2026-03-02.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F5"/>
+  <dimension ref="A1:F2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -451,104 +451,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Hacks Home Design</t>
+          <t>Grafix River</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>18300</v>
+        <v>3300</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2026-01-25</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
-          <t>https://youtube.com/channel/UCMnEb6Z65tA86a37g0EEn0w</t>
+          <t>https://youtube.com/channel/UCSqbqou3vR0X4Ig_CDMwxzA</t>
         </is>
       </c>
       <c r="F2">
-        <f>HYPERLINK("mailto:?subject=Collab%20Proposal%3A%20AI%203D%20Tools%20for%20your%20Audience&amp;body=Hi%20Hacks%20Home%20Design%2C%0A%0ALove%20your%20content%21%20I%27m%20Nemo%20from%20Pacdora...", "Click to Email")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Frame of Faizan</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
-        <v>8890</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>2026-02-27</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>faiz4976@gmail.com</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>https://youtube.com/channel/UC3i5ZyKMg780BidcDMm9FeA</t>
-        </is>
-      </c>
-      <c r="F3">
-        <f>HYPERLINK("mailto:?subject=Collab%20Proposal%3A%20AI%203D%20Tools%20for%20your%20Audience&amp;body=Hi%20Frame%20of%20Faizan%2C%0A%0ALove%20your%20content%21%20I%27m%20Nemo%20from%20Pacdora...", "Click to Email")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Nexo Creative</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
-        <v>2100</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>2026-03-02</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr"/>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>https://youtube.com/channel/UCTvs4AWdZRBXrD-M_K19n-A</t>
-        </is>
-      </c>
-      <c r="F4">
-        <f>HYPERLINK("mailto:?subject=Collab%20Proposal%3A%20AI%203D%20Tools%20for%20your%20Audience&amp;body=Hi%20Nexo%20Creative%2C%0A%0ALove%20your%20content%21%20I%27m%20Nemo%20from%20Pacdora...", "Click to Email")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>josieharrisondotcom</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
-        <v>1020</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>2026-03-01</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr"/>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>https://youtube.com/channel/UCHEXXych-Yx9leQzvP4QJqQ</t>
-        </is>
-      </c>
-      <c r="F5">
-        <f>HYPERLINK("mailto:?subject=Collab%20Proposal%3A%20AI%203D%20Tools%20for%20your%20Audience&amp;body=Hi%20josieharrisondotcom%2C%0A%0ALove%20your%20content%21%20I%27m%20Nemo%20from%20Pacdora...", "Click to Email")</f>
+        <f>HYPERLINK("mailto:?subject=Collab%20Proposal%3A%20AI%203D%20Tools%20for%20your%20Audience&amp;body=Hi%20Grafix%20River%2C%0A%0ALove%20your%20content%21%20I%27m%20Nemo%20from%20Pacdora...", "Click to Email")</f>
         <v/>
       </c>
     </row>
